--- a/artfynd/A 31714-2023 artfynd.xlsx
+++ b/artfynd/A 31714-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129949405</v>
       </c>
       <c r="B2" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129949410</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31714-2023 artfynd.xlsx
+++ b/artfynd/A 31714-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129949405</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129949410</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31714-2023 artfynd.xlsx
+++ b/artfynd/A 31714-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129949405</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129949410</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31714-2023 artfynd.xlsx
+++ b/artfynd/A 31714-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129949405</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129949410</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31714-2023 artfynd.xlsx
+++ b/artfynd/A 31714-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129949405</v>
+        <v>129949403</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>355947</v>
+        <v>355963</v>
       </c>
       <c r="R2" t="n">
-        <v>6392830</v>
+        <v>6392715</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På flera högstubbar och döda rakor av tall i området.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,14 +777,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129949410</v>
+        <v>129949405</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>355904</v>
+        <v>355947</v>
       </c>
       <c r="R3" t="n">
-        <v>6392840</v>
+        <v>6392830</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,6 +855,11 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På flera högstubbar och döda rakor av tall i området.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -881,6 +881,424 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129949406</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bollebygd kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>355966</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6392721</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129949410</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bollebygd kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>355904</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6392840</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129949411</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bollebygd kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>355939</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6392763</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spår av Spillkråka på flera högstubbar av tall.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127800349</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bollebygd, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>355967</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6392883</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31714-2023 artfynd.xlsx
+++ b/artfynd/A 31714-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129949403</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129949405</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129949406</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129949410</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129949411</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,8 +1329,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127800349</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>